--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -1,40 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <color theme="1"/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -52,17 +46,81 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -350,32 +408,41 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E138"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F138"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1">
+      <c r="A1" t="inlineStr">
         <is>
           <t>species_sci</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>specimen_key</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>museum</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Manipulability_index</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Workspace</t>
         </is>
@@ -392,10 +459,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D2">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>AMNH 204072</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>0.0171</v>
       </c>
-      <c r="E2">
+      <c r="F2" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -410,10 +487,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>AMNH 172124</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
         <v>0.0161</v>
       </c>
-      <c r="E3">
+      <c r="F3" t="n">
         <v>0.0236</v>
       </c>
     </row>
@@ -428,10 +515,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>WITS 1301</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
         <v>0.0167</v>
       </c>
-      <c r="E4">
+      <c r="F4" t="n">
         <v>0.0246</v>
       </c>
     </row>
@@ -446,10 +543,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>WITS 1408</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
         <v>0.0155</v>
       </c>
-      <c r="E5">
+      <c r="F5" t="n">
         <v>0.0244</v>
       </c>
     </row>
@@ -464,10 +571,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>WITS 1501</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
         <v>0.0167</v>
       </c>
-      <c r="E6">
+      <c r="F6" t="n">
         <v>0.0245</v>
       </c>
     </row>
@@ -482,10 +599,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WITS 1576</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
         <v>0.0177</v>
       </c>
-      <c r="E7">
+      <c r="F7" t="n">
         <v>0.0257</v>
       </c>
     </row>
@@ -500,10 +627,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>WITS 1689</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>0.0182</v>
       </c>
-      <c r="E8">
+      <c r="F8" t="n">
         <v>0.0267</v>
       </c>
     </row>
@@ -518,10 +655,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>WITS 1791</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
         <v>0.0177</v>
       </c>
-      <c r="E9">
+      <c r="F9" t="n">
         <v>0.0267</v>
       </c>
     </row>
@@ -536,10 +683,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>WITS 1918</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
         <v>0.0183</v>
       </c>
-      <c r="E10">
+      <c r="F10" t="n">
         <v>0.0273</v>
       </c>
     </row>
@@ -554,10 +711,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WITS 1925</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
         <v>0.0149</v>
       </c>
-      <c r="E11">
+      <c r="F11" t="n">
         <v>0.0224</v>
       </c>
     </row>
@@ -572,10 +739,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>WITS 1947</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
         <v>0.018</v>
       </c>
-      <c r="E12">
+      <c r="F12" t="n">
         <v>0.0262</v>
       </c>
     </row>
@@ -590,10 +767,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>WITS 2012</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
         <v>0.0172</v>
       </c>
-      <c r="E13">
+      <c r="F13" t="n">
         <v>0.0252</v>
       </c>
     </row>
@@ -608,10 +795,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>WITS 2087</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
         <v>0.0153</v>
       </c>
-      <c r="E14">
+      <c r="F14" t="n">
         <v>0.0229</v>
       </c>
     </row>
@@ -626,10 +823,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WITS 2191</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
         <v>0.0162</v>
       </c>
-      <c r="E15">
+      <c r="F15" t="n">
         <v>0.0244</v>
       </c>
     </row>
@@ -644,10 +851,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WITS 3156</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
         <v>0.0173</v>
       </c>
-      <c r="E16">
+      <c r="F16" t="n">
         <v>0.0253</v>
       </c>
     </row>
@@ -662,10 +879,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WITS 3314</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>0.0174</v>
       </c>
-      <c r="E17">
+      <c r="F17" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -680,10 +907,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>WITS 3316</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
         <v>0.0154</v>
       </c>
-      <c r="E18">
+      <c r="F18" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -698,10 +935,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>WITS 3360</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
         <v>0.0168</v>
       </c>
-      <c r="E19">
+      <c r="F19" t="n">
         <v>0.0259</v>
       </c>
     </row>
@@ -716,10 +963,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>WITS 3364</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
         <v>0.0185</v>
       </c>
-      <c r="E20">
+      <c r="F20" t="n">
         <v>0.0269</v>
       </c>
     </row>
@@ -734,10 +991,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>WITS 3369</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
         <v>0.0172</v>
       </c>
-      <c r="E21">
+      <c r="F21" t="n">
         <v>0.0256</v>
       </c>
     </row>
@@ -752,10 +1019,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>WITS 3372</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
         <v>0.0151</v>
       </c>
-      <c r="E22">
+      <c r="F22" t="n">
         <v>0.0224</v>
       </c>
     </row>
@@ -770,10 +1047,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>WITS 3388</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
         <v>0.0167</v>
       </c>
-      <c r="E23">
+      <c r="F23" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -788,10 +1075,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>WITS 3448</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
         <v>0.0173</v>
       </c>
-      <c r="E24">
+      <c r="F24" t="n">
         <v>0.0259</v>
       </c>
     </row>
@@ -806,10 +1103,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>WITS 3664</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
         <v>0.0192</v>
       </c>
-      <c r="E25">
+      <c r="F25" t="n">
         <v>0.0279</v>
       </c>
     </row>
@@ -824,10 +1131,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>WITS 3529</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
         <v>0.0174</v>
       </c>
-      <c r="E26">
+      <c r="F26" t="n">
         <v>0.0262</v>
       </c>
     </row>
@@ -842,10 +1159,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>WITS 3606</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
         <v>0.0175</v>
       </c>
-      <c r="E27">
+      <c r="F27" t="n">
         <v>0.0256</v>
       </c>
     </row>
@@ -860,10 +1187,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>WITS 178</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
         <v>0.0167</v>
       </c>
-      <c r="E28">
+      <c r="F28" t="n">
         <v>0.0251</v>
       </c>
     </row>
@@ -878,10 +1215,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>WITS 188</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
         <v>0.0173</v>
       </c>
-      <c r="E29">
+      <c r="F29" t="n">
         <v>0.0259</v>
       </c>
     </row>
@@ -896,10 +1243,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>WITS 1472</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
         <v>0.0166</v>
       </c>
-      <c r="E30">
+      <c r="F30" t="n">
         <v>0.0255</v>
       </c>
     </row>
@@ -914,10 +1271,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>WITS 2097</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
         <v>0.0176</v>
       </c>
-      <c r="E31">
+      <c r="F31" t="n">
         <v>0.0256</v>
       </c>
     </row>
@@ -932,10 +1299,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>WITS 906</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>WITS</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
         <v>0.0185</v>
       </c>
-      <c r="E32">
+      <c r="F32" t="n">
         <v>0.0271</v>
       </c>
     </row>
@@ -950,10 +1327,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>UV S22</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
         <v>0.0181</v>
       </c>
-      <c r="E33">
+      <c r="F33" t="n">
         <v>0.0269</v>
       </c>
     </row>
@@ -968,10 +1355,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>UV S45</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
         <v>0.0165</v>
       </c>
-      <c r="E34">
+      <c r="F34" t="n">
         <v>0.0245</v>
       </c>
     </row>
@@ -986,10 +1383,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>UV S56</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
         <v>0.017</v>
       </c>
-      <c r="E35">
+      <c r="F35" t="n">
         <v>0.0248</v>
       </c>
     </row>
@@ -1004,10 +1411,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>UV S54</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
         <v>0.0176</v>
       </c>
-      <c r="E36">
+      <c r="F36" t="n">
         <v>0.0266</v>
       </c>
     </row>
@@ -1022,10 +1439,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>UV S59</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
         <v>0.0178</v>
       </c>
-      <c r="E37">
+      <c r="F37" t="n">
         <v>0.0264</v>
       </c>
     </row>
@@ -1040,10 +1467,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>UV S38</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
         <v>0.0183</v>
       </c>
-      <c r="E38">
+      <c r="F38" t="n">
         <v>0.0272</v>
       </c>
     </row>
@@ -1058,10 +1495,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>UV S7</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
         <v>0.018</v>
       </c>
-      <c r="E39">
+      <c r="F39" t="n">
         <v>0.0275</v>
       </c>
     </row>
@@ -1076,10 +1523,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>UV S26</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
         <v>0.0175</v>
       </c>
-      <c r="E40">
+      <c r="F40" t="n">
         <v>0.026</v>
       </c>
     </row>
@@ -1094,10 +1551,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>UV S17</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
         <v>0.0153</v>
       </c>
-      <c r="E41">
+      <c r="F41" t="n">
         <v>0.0231</v>
       </c>
     </row>
@@ -1112,10 +1579,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>UV S52</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>UV</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
         <v>0.017</v>
       </c>
-      <c r="E42">
+      <c r="F42" t="n">
         <v>0.0257</v>
       </c>
     </row>
@@ -1130,10 +1607,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>UNI-FI 4865</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>UNI-FI</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
         <v>0.0162</v>
       </c>
-      <c r="E43">
+      <c r="F43" t="n">
         <v>0.0247</v>
       </c>
     </row>
@@ -1148,10 +1635,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>UNI-FI 4887</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>UNI-FI</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
         <v>0.0158</v>
       </c>
-      <c r="E44">
+      <c r="F44" t="n">
         <v>0.0238</v>
       </c>
     </row>
@@ -1166,10 +1663,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>UNI-FI 4868</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>UNI-FI</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
         <v>0.0144</v>
       </c>
-      <c r="E45">
+      <c r="F45" t="n">
         <v>0.0219</v>
       </c>
     </row>
@@ -1184,10 +1691,20 @@
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="D46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>UNI-FI 4880</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>UNI-FI</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
         <v>0.0167</v>
       </c>
-      <c r="E46">
+      <c r="F46" t="n">
         <v>0.0244</v>
       </c>
     </row>
@@ -1202,10 +1719,20 @@
           <t>Pan troglodytes</t>
         </is>
       </c>
-      <c r="D47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>AMNH 89351</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
         <v>0.0055</v>
       </c>
-      <c r="E47">
+      <c r="F47" t="n">
         <v>0.0092</v>
       </c>
     </row>
@@ -1220,10 +1747,20 @@
           <t>Pan troglodytes</t>
         </is>
       </c>
-      <c r="D48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>AMNH 89353</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
         <v>0.0052</v>
       </c>
-      <c r="E48">
+      <c r="F48" t="n">
         <v>0.0089</v>
       </c>
     </row>
@@ -1238,10 +1775,20 @@
           <t>Pan troglodytes</t>
         </is>
       </c>
-      <c r="D49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>AMNH 89355</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
         <v>0.0072</v>
       </c>
-      <c r="E49">
+      <c r="F49" t="n">
         <v>0.0112</v>
       </c>
     </row>
@@ -1256,10 +1803,20 @@
           <t>Pan troglodytes</t>
         </is>
       </c>
-      <c r="D50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>AMNH 90189</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
         <v>0.0065</v>
       </c>
-      <c r="E50">
+      <c r="F50" t="n">
         <v>0.0105</v>
       </c>
     </row>
@@ -1274,10 +1831,20 @@
           <t>Pan troglodytes</t>
         </is>
       </c>
-      <c r="D51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HMNH 11772</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
         <v>0.0065</v>
       </c>
-      <c r="E51">
+      <c r="F51" t="n">
         <v>0.0104</v>
       </c>
     </row>
@@ -1292,10 +1859,20 @@
           <t>Pan troglodytes</t>
         </is>
       </c>
-      <c r="D52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>NMW 25124</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
         <v>0.0053</v>
       </c>
-      <c r="E52">
+      <c r="F52" t="n">
         <v>0.008999999999999999</v>
       </c>
     </row>
@@ -1310,10 +1887,20 @@
           <t>Pan troglodytes</t>
         </is>
       </c>
-      <c r="D53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>NMW 13528</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
         <v>0.0037</v>
       </c>
-      <c r="E53">
+      <c r="F53" t="n">
         <v>0.0068</v>
       </c>
     </row>
@@ -1328,10 +1915,20 @@
           <t>Pan paniscus</t>
         </is>
       </c>
-      <c r="D54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>MRAC 29052</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>MRAC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
         <v>0.0078</v>
       </c>
-      <c r="E54">
+      <c r="F54" t="n">
         <v>0.0121</v>
       </c>
     </row>
@@ -1346,10 +1943,20 @@
           <t>Pan paniscus</t>
         </is>
       </c>
-      <c r="D55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>MRAC 29044</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>MRAC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
         <v>0.0062</v>
       </c>
-      <c r="E55">
+      <c r="F55" t="n">
         <v>0.0103</v>
       </c>
     </row>
@@ -1364,10 +1971,20 @@
           <t>Pan paniscus</t>
         </is>
       </c>
-      <c r="D56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>MRAC 27696</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>MRAC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
         <v>0.0047</v>
       </c>
-      <c r="E56">
+      <c r="F56" t="n">
         <v>0.0083</v>
       </c>
     </row>
@@ -1382,10 +1999,20 @@
           <t>Pan paniscus</t>
         </is>
       </c>
-      <c r="D57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MRAC 29042</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>MRAC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
         <v>0.008800000000000001</v>
       </c>
-      <c r="E57">
+      <c r="F57" t="n">
         <v>0.0135</v>
       </c>
     </row>
@@ -1400,10 +2027,20 @@
           <t>Pan paniscus</t>
         </is>
       </c>
-      <c r="D58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MRAC 29045</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>MRAC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
         <v>0.0063</v>
       </c>
-      <c r="E58">
+      <c r="F58" t="n">
         <v>0.0102</v>
       </c>
     </row>
@@ -1418,10 +2055,20 @@
           <t>Gorilla gorilla</t>
         </is>
       </c>
-      <c r="D59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>AMNH 81652</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
         <v>0.008500000000000001</v>
       </c>
-      <c r="E59">
+      <c r="F59" t="n">
         <v>0.0127</v>
       </c>
     </row>
@@ -1436,10 +2083,20 @@
           <t>Gorilla gorilla</t>
         </is>
       </c>
-      <c r="D60">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>AMNH 90194</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="E60">
+      <c r="F60" t="n">
         <v>0.0124</v>
       </c>
     </row>
@@ -1454,10 +2111,20 @@
           <t>Gorilla gorilla</t>
         </is>
       </c>
-      <c r="D61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ZMB 18515</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ZMB</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
         <v>0.0092</v>
       </c>
-      <c r="E61">
+      <c r="F61" t="n">
         <v>0.0128</v>
       </c>
     </row>
@@ -1472,10 +2139,20 @@
           <t>Gorilla gorilla</t>
         </is>
       </c>
-      <c r="D62">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NMW 792</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="E62">
+      <c r="F62" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -1490,10 +2167,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D63">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>AMNH 18010</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
         <v>0.0003</v>
       </c>
-      <c r="E63">
+      <c r="F63" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -1508,10 +2195,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D64">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>AMNH 200898</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
         <v>0.0025</v>
       </c>
-      <c r="E64">
+      <c r="F64" t="n">
         <v>0.0052</v>
       </c>
     </row>
@@ -1526,10 +2223,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D65">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>AMNH 90395</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
         <v>0.0001</v>
       </c>
-      <c r="E65">
+      <c r="F65" t="n">
         <v>0.0004</v>
       </c>
     </row>
@@ -1544,10 +2251,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D66">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HMNH 5154</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
         <v>0.0012</v>
       </c>
-      <c r="E66">
+      <c r="F66" t="n">
         <v>0.003</v>
       </c>
     </row>
@@ -1562,10 +2279,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D67">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>NMW 798</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
         <v>0.0014</v>
       </c>
-      <c r="E67">
+      <c r="F67" t="n">
         <v>0.0036</v>
       </c>
     </row>
@@ -1580,10 +2307,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D68">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>NMW 795</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
         <v>0</v>
       </c>
-      <c r="E68">
+      <c r="F68" t="n">
         <v>0.0002</v>
       </c>
     </row>
@@ -1598,10 +2335,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D69">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>NMW 797</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="E69">
+      <c r="F69" t="n">
         <v>0.0019</v>
       </c>
     </row>
@@ -1616,10 +2363,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D70">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>NMW 800/B 5414</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
         <v>0.0014</v>
       </c>
-      <c r="E70">
+      <c r="F70" t="n">
         <v>0.0034</v>
       </c>
     </row>
@@ -1634,10 +2391,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NMW 654</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
         <v>0.0003</v>
       </c>
-      <c r="E71">
+      <c r="F71" t="n">
         <v>0.001</v>
       </c>
     </row>
@@ -1652,10 +2419,20 @@
           <t>Pongo pygmaeus</t>
         </is>
       </c>
-      <c r="D72">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>NMW 799</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
         <v>0.0017</v>
       </c>
-      <c r="E72">
+      <c r="F72" t="n">
         <v>0.0038</v>
       </c>
     </row>
@@ -1670,10 +2447,20 @@
           <t>Hylobates lar</t>
         </is>
       </c>
-      <c r="D73">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HMNH 35945</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
         <v>0.0044</v>
       </c>
-      <c r="E73">
+      <c r="F73" t="n">
         <v>0.0075</v>
       </c>
     </row>
@@ -1688,10 +2475,20 @@
           <t>Hylobates lar</t>
         </is>
       </c>
-      <c r="D74">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HMNH 41421</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
         <v>0.0025</v>
       </c>
-      <c r="E74">
+      <c r="F74" t="n">
         <v>0.0048</v>
       </c>
     </row>
@@ -1706,10 +2503,20 @@
           <t>Hylobates lar</t>
         </is>
       </c>
-      <c r="D75">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HMNH 41476</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
         <v>0.0035</v>
       </c>
-      <c r="E75">
+      <c r="F75" t="n">
         <v>0.0065</v>
       </c>
     </row>
@@ -1724,10 +2531,20 @@
           <t>Hylobates lar</t>
         </is>
       </c>
-      <c r="D76">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HMNH 41504</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
         <v>0.0039</v>
       </c>
-      <c r="E76">
+      <c r="F76" t="n">
         <v>0.007</v>
       </c>
     </row>
@@ -1742,10 +2559,20 @@
           <t>Hylobates lar</t>
         </is>
       </c>
-      <c r="D77">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HMNH 41537</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
         <v>0.0043</v>
       </c>
-      <c r="E77">
+      <c r="F77" t="n">
         <v>0.0077</v>
       </c>
     </row>
@@ -1760,10 +2587,20 @@
           <t>Macaca mulatta</t>
         </is>
       </c>
-      <c r="D78">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>UM-APC 319</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
         <v>0.01</v>
       </c>
-      <c r="E78">
+      <c r="F78" t="n">
         <v>0.0155</v>
       </c>
     </row>
@@ -1778,10 +2615,20 @@
           <t>Macaca mulatta</t>
         </is>
       </c>
-      <c r="D79">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>UM-APC 279</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
         <v>0.0076</v>
       </c>
-      <c r="E79">
+      <c r="F79" t="n">
         <v>0.0129</v>
       </c>
     </row>
@@ -1796,10 +2643,20 @@
           <t>Macaca mulatta</t>
         </is>
       </c>
-      <c r="D80">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>UM-APC 318</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
         <v>0.0076</v>
       </c>
-      <c r="E80">
+      <c r="F80" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -1814,10 +2671,20 @@
           <t>Macaca mulatta</t>
         </is>
       </c>
-      <c r="D81">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>UM-APC 320</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
         <v>0.0086</v>
       </c>
-      <c r="E81">
+      <c r="F81" t="n">
         <v>0.0134</v>
       </c>
     </row>
@@ -1832,10 +2699,20 @@
           <t>Macaca mulatta</t>
         </is>
       </c>
-      <c r="D82">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>UM-APC 224</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="E82">
+      <c r="F82" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -1850,10 +2727,20 @@
           <t>Macaca mulatta</t>
         </is>
       </c>
-      <c r="D83">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>UM-APC 286</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
         <v>0.0039</v>
       </c>
-      <c r="E83">
+      <c r="F83" t="n">
         <v>0.0074</v>
       </c>
     </row>
@@ -1868,10 +2755,20 @@
           <t>Macaca mulatta</t>
         </is>
       </c>
-      <c r="D84">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>UM-APC 231</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
         <v>0.008500000000000001</v>
       </c>
-      <c r="E84">
+      <c r="F84" t="n">
         <v>0.0156</v>
       </c>
     </row>
@@ -1886,10 +2783,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D85">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>UM-APC 217</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
         <v>0.0076</v>
       </c>
-      <c r="E85">
+      <c r="F85" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -1904,10 +2811,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D86">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>UM-APC 281</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>UM-APC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
         <v>0.009599999999999999</v>
       </c>
-      <c r="E86">
+      <c r="F86" t="n">
         <v>0.0148</v>
       </c>
     </row>
@@ -1922,10 +2839,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D87">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HMNH 35611</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
         <v>0.0081</v>
       </c>
-      <c r="E87">
+      <c r="F87" t="n">
         <v>0.0127</v>
       </c>
     </row>
@@ -1940,10 +2867,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D88">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>HMNH 35612</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="E88">
+      <c r="F88" t="n">
         <v>0.0128</v>
       </c>
     </row>
@@ -1958,10 +2895,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D89">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HMNH 35656</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
         <v>0.008500000000000001</v>
       </c>
-      <c r="E89">
+      <c r="F89" t="n">
         <v>0.0135</v>
       </c>
     </row>
@@ -1976,10 +2923,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D90">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>HMNH 35658</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
         <v>0.0081</v>
       </c>
-      <c r="E90">
+      <c r="F90" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -1994,10 +2951,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D91">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>HMNH 35694</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
         <v>0.0077</v>
       </c>
-      <c r="E91">
+      <c r="F91" t="n">
         <v>0.0124</v>
       </c>
     </row>
@@ -2012,10 +2979,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D92">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HMNH 35729</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="E92">
+      <c r="F92" t="n">
         <v>0.0131</v>
       </c>
     </row>
@@ -2030,10 +3007,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D93">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>HMNH 35727</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
         <v>0.0071</v>
       </c>
-      <c r="E93">
+      <c r="F93" t="n">
         <v>0.0115</v>
       </c>
     </row>
@@ -2048,10 +3035,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D94">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HMNH 35736</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
         <v>0.008399999999999999</v>
       </c>
-      <c r="E94">
+      <c r="F94" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -2066,10 +3063,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D95">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HMNH 35735</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
         <v>0.0073</v>
       </c>
-      <c r="E95">
+      <c r="F95" t="n">
         <v>0.0121</v>
       </c>
     </row>
@@ -2084,10 +3091,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D96">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>HMNH 37349</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
         <v>0.0073</v>
       </c>
-      <c r="E96">
+      <c r="F96" t="n">
         <v>0.0122</v>
       </c>
     </row>
@@ -2102,10 +3119,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D97">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HMNH 37406</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
         <v>0.0062</v>
       </c>
-      <c r="E97">
+      <c r="F97" t="n">
         <v>0.0111</v>
       </c>
     </row>
@@ -2120,10 +3147,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D98">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HMNH 37407</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
         <v>0.0058</v>
       </c>
-      <c r="E98">
+      <c r="F98" t="n">
         <v>0.0104</v>
       </c>
     </row>
@@ -2138,10 +3175,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D99">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>HMNH 37415</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
         <v>0.0072</v>
       </c>
-      <c r="E99">
+      <c r="F99" t="n">
         <v>0.0123</v>
       </c>
     </row>
@@ -2156,10 +3203,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D100">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>HMNH 37416</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
         <v>0.007900000000000001</v>
       </c>
-      <c r="E100">
+      <c r="F100" t="n">
         <v>0.0131</v>
       </c>
     </row>
@@ -2174,10 +3231,20 @@
           <t>Macaca fascicularis</t>
         </is>
       </c>
-      <c r="D101">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>HMNH 57836</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
         <v>0.0081</v>
       </c>
-      <c r="E101">
+      <c r="F101" t="n">
         <v>0.013</v>
       </c>
     </row>
@@ -2192,10 +3259,20 @@
           <t>Papio hamadryas</t>
         </is>
       </c>
-      <c r="D102">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AMNH 200847</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
         <v>0.0134</v>
       </c>
-      <c r="E102">
+      <c r="F102" t="n">
         <v>0.0188</v>
       </c>
     </row>
@@ -2210,10 +3287,20 @@
           <t>Papio hamadryas</t>
         </is>
       </c>
-      <c r="D103">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>NMW 772</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
         <v>0.0118</v>
       </c>
-      <c r="E103">
+      <c r="F103" t="n">
         <v>0.0165</v>
       </c>
     </row>
@@ -2228,10 +3315,20 @@
           <t>Papio hamadryas</t>
         </is>
       </c>
-      <c r="D104">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>NMW 825</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
         <v>0.0133</v>
       </c>
-      <c r="E104">
+      <c r="F104" t="n">
         <v>0.0194</v>
       </c>
     </row>
@@ -2246,10 +3343,20 @@
           <t>Papio hamadryas</t>
         </is>
       </c>
-      <c r="D105">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>NMW 847</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
         <v>0.0117</v>
       </c>
-      <c r="E105">
+      <c r="F105" t="n">
         <v>0.0173</v>
       </c>
     </row>
@@ -2264,10 +3371,20 @@
           <t>Papio hamadryas</t>
         </is>
       </c>
-      <c r="D106">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>NMW 28584</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
         <v>0.0135</v>
       </c>
-      <c r="E106">
+      <c r="F106" t="n">
         <v>0.0188</v>
       </c>
     </row>
@@ -2282,10 +3399,20 @@
           <t>Papio hamadryas</t>
         </is>
       </c>
-      <c r="D107">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>NMW 43411</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
         <v>0.0123</v>
       </c>
-      <c r="E107">
+      <c r="F107" t="n">
         <v>0.0173</v>
       </c>
     </row>
@@ -2300,10 +3427,20 @@
           <t>Papio hamadryas</t>
         </is>
       </c>
-      <c r="D108">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>NMW 22755</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NMW</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
         <v>0.012</v>
       </c>
-      <c r="E108">
+      <c r="F108" t="n">
         <v>0.0174</v>
       </c>
     </row>
@@ -2318,10 +3455,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D109">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>HMNH 35666</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
         <v>0.0035</v>
       </c>
-      <c r="E109">
+      <c r="F109" t="n">
         <v>0.0065</v>
       </c>
     </row>
@@ -2336,10 +3483,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D110">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>HMNH 35669</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
         <v>0.003</v>
       </c>
-      <c r="E110">
+      <c r="F110" t="n">
         <v>0.0059</v>
       </c>
     </row>
@@ -2354,10 +3511,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D111">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>HMNH 35640</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
         <v>0.0026</v>
       </c>
-      <c r="E111">
+      <c r="F111" t="n">
         <v>0.0053</v>
       </c>
     </row>
@@ -2372,10 +3539,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D112">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>HMNH 35678</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
         <v>0.0022</v>
       </c>
-      <c r="E112">
+      <c r="F112" t="n">
         <v>0.0046</v>
       </c>
     </row>
@@ -2390,10 +3567,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D113">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>HMNH 35675</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
         <v>0.0022</v>
       </c>
-      <c r="E113">
+      <c r="F113" t="n">
         <v>0.0045</v>
       </c>
     </row>
@@ -2408,10 +3595,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D114">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>HMNH 35688</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
         <v>0.0017</v>
       </c>
-      <c r="E114">
+      <c r="F114" t="n">
         <v>0.0037</v>
       </c>
     </row>
@@ -2426,10 +3623,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D115">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>HMNH 35683</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
         <v>0.0015</v>
       </c>
-      <c r="E115">
+      <c r="F115" t="n">
         <v>0.0033</v>
       </c>
     </row>
@@ -2444,10 +3651,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D116">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>HMNH 37396</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
         <v>0.0038</v>
       </c>
-      <c r="E116">
+      <c r="F116" t="n">
         <v>0.0069</v>
       </c>
     </row>
@@ -2462,10 +3679,20 @@
           <t>Presbytis cristata</t>
         </is>
       </c>
-      <c r="D117">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>HMNH 37665</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
         <v>0.0012</v>
       </c>
-      <c r="E117">
+      <c r="F117" t="n">
         <v>0.0029</v>
       </c>
     </row>
@@ -2480,10 +3707,20 @@
           <t>Sapajus apella</t>
         </is>
       </c>
-      <c r="D118">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>AMNH 188037</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
         <v>0.013</v>
       </c>
-      <c r="E118">
+      <c r="F118" t="n">
         <v>0.0216</v>
       </c>
     </row>
@@ -2498,10 +3735,20 @@
           <t>Sapajus apella</t>
         </is>
       </c>
-      <c r="D119">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>AMNH 95129</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
         <v>0.0108</v>
       </c>
-      <c r="E119">
+      <c r="F119" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -2516,10 +3763,20 @@
           <t>Sapajus apella</t>
         </is>
       </c>
-      <c r="D120">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>AMNH 80169</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
         <v>0.0109</v>
       </c>
-      <c r="E120">
+      <c r="F120" t="n">
         <v>0.0183</v>
       </c>
     </row>
@@ -2534,10 +3791,20 @@
           <t>Sapajus apella</t>
         </is>
       </c>
-      <c r="D121">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>HMNH 61405</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>HMNH</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
         <v>0.0073</v>
       </c>
-      <c r="E121">
+      <c r="F121" t="n">
         <v>0.0122</v>
       </c>
     </row>
@@ -2552,10 +3819,20 @@
           <t>Sapajus apella</t>
         </is>
       </c>
-      <c r="D122">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>YPM MAM 7577</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>YPM</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
         <v>0.0073</v>
       </c>
-      <c r="E122">
+      <c r="F122" t="n">
         <v>0.0125</v>
       </c>
     </row>
@@ -2570,10 +3847,20 @@
           <t>Sapajus apella</t>
         </is>
       </c>
-      <c r="D123">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>YPM MAM 6873</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>YPM</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
         <v>0.0134</v>
       </c>
-      <c r="E123">
+      <c r="F123" t="n">
         <v>0.0224</v>
       </c>
     </row>
@@ -2588,10 +3875,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D124">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>AMNH 15485</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
         <v>0.0144</v>
       </c>
-      <c r="E124">
+      <c r="F124" t="n">
         <v>0.0221</v>
       </c>
     </row>
@@ -2606,10 +3903,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D125">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>AMNH 23403</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
         <v>0.0129</v>
       </c>
-      <c r="E125">
+      <c r="F125" t="n">
         <v>0.0204</v>
       </c>
     </row>
@@ -2624,10 +3931,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D126">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>AMNH 23401</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
         <v>0.0128</v>
       </c>
-      <c r="E126">
+      <c r="F126" t="n">
         <v>0.0216</v>
       </c>
     </row>
@@ -2642,10 +3959,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D127">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>AMNH 23399</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
         <v>0.0118</v>
       </c>
-      <c r="E127">
+      <c r="F127" t="n">
         <v>0.0202</v>
       </c>
     </row>
@@ -2660,10 +3987,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D128">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMNH 15484</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
         <v>0.0122</v>
       </c>
-      <c r="E128">
+      <c r="F128" t="n">
         <v>0.0189</v>
       </c>
     </row>
@@ -2678,10 +4015,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D129">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AMNH 200753</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
         <v>0.0118</v>
       </c>
-      <c r="E129">
+      <c r="F129" t="n">
         <v>0.019</v>
       </c>
     </row>
@@ -2696,10 +4043,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D130">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>AMNH 14017</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
         <v>0.0118</v>
       </c>
-      <c r="E130">
+      <c r="F130" t="n">
         <v>0.0202</v>
       </c>
     </row>
@@ -2714,10 +4071,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D131">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>AMNH 201434</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
         <v>0.0105</v>
       </c>
-      <c r="E131">
+      <c r="F131" t="n">
         <v>0.018</v>
       </c>
     </row>
@@ -2732,10 +4099,20 @@
           <t>Cebus albifrons</t>
         </is>
       </c>
-      <c r="D132">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>AMNH 201288</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
         <v>0.013</v>
       </c>
-      <c r="E132">
+      <c r="F132" t="n">
         <v>0.0213</v>
       </c>
     </row>
@@ -2750,10 +4127,20 @@
           <t>Alouatta seniculus</t>
         </is>
       </c>
-      <c r="D133">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>AMNH 23330</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
         <v>0.008200000000000001</v>
       </c>
-      <c r="E133">
+      <c r="F133" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -2768,10 +4155,20 @@
           <t>Alouatta seniculus</t>
         </is>
       </c>
-      <c r="D134">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>AMNH 23334</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
         <v>0.0086</v>
       </c>
-      <c r="E134">
+      <c r="F134" t="n">
         <v>0.0162</v>
       </c>
     </row>
@@ -2786,10 +4183,20 @@
           <t>Alouatta seniculus</t>
         </is>
       </c>
-      <c r="D135">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>AMNH 23337</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
         <v>0.008699999999999999</v>
       </c>
-      <c r="E135">
+      <c r="F135" t="n">
         <v>0.0169</v>
       </c>
     </row>
@@ -2804,10 +4211,20 @@
           <t>Alouatta seniculus</t>
         </is>
       </c>
-      <c r="D136">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>AMNH 23335</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
         <v>0.0097</v>
       </c>
-      <c r="E136">
+      <c r="F136" t="n">
         <v>0.0181</v>
       </c>
     </row>
@@ -2822,10 +4239,20 @@
           <t>Alouatta seniculus</t>
         </is>
       </c>
-      <c r="D137">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>AMNH 23329</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
         <v>0.0089</v>
       </c>
-      <c r="E137">
+      <c r="F137" t="n">
         <v>0.0169</v>
       </c>
     </row>
@@ -2840,15 +4267,25 @@
           <t>Alouatta seniculus</t>
         </is>
       </c>
-      <c r="D138">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>AMNH 14660</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AMNH</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
         <v>0.0091</v>
       </c>
-      <c r="E138">
+      <c r="F138" t="n">
         <v>0.0172</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -3128,13 +4565,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18589848-7020-4422-BC67-F85104C88BDB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E847A7-E41A-40FE-A6C8-3A31F8569A42}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C64033FA-82CB-4F8A-A968-172AA40A4F44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CD27C9B-3C50-48E1-883F-FBD466CD3328}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{730FC0E8-C165-4035-9430-A02852EA92AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{564F5D96-EC9D-4760-ADA9-6922E09E2A9C}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -1,34 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,81 +52,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,41 +350,37 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F138"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>species_sci</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Species</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>specimen_key</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>museum</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Manipulability_index</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Workspace</t>
         </is>
@@ -469,10 +407,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.0171</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.025</v>
       </c>
     </row>
@@ -497,10 +435,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.0161</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.0236</v>
       </c>
     </row>
@@ -525,10 +463,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.0167</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.0246</v>
       </c>
     </row>
@@ -553,10 +491,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.0155</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.0244</v>
       </c>
     </row>
@@ -581,10 +519,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.0167</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.0245</v>
       </c>
     </row>
@@ -609,10 +547,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0.0177</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.0257</v>
       </c>
     </row>
@@ -637,10 +575,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>0.0182</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>0.0267</v>
       </c>
     </row>
@@ -665,10 +603,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>0.0177</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>0.0267</v>
       </c>
     </row>
@@ -693,10 +631,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>0.0183</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>0.0273</v>
       </c>
     </row>
@@ -721,10 +659,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>0.0149</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>0.0224</v>
       </c>
     </row>
@@ -749,10 +687,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0.018</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0.0262</v>
       </c>
     </row>
@@ -777,10 +715,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>0.0172</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.0252</v>
       </c>
     </row>
@@ -805,10 +743,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>0.0153</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>0.0229</v>
       </c>
     </row>
@@ -833,10 +771,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>0.0162</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.0244</v>
       </c>
     </row>
@@ -861,10 +799,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>0.0173</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>0.0253</v>
       </c>
     </row>
@@ -889,10 +827,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0.0174</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0.026</v>
       </c>
     </row>
@@ -917,10 +855,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>0.0154</v>
       </c>
-      <c r="F18" t="n">
+      <c r="F18">
         <v>0.0231</v>
       </c>
     </row>
@@ -945,10 +883,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19">
         <v>0.0168</v>
       </c>
-      <c r="F19" t="n">
+      <c r="F19">
         <v>0.0259</v>
       </c>
     </row>
@@ -973,10 +911,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E20" t="n">
+      <c r="E20">
         <v>0.0185</v>
       </c>
-      <c r="F20" t="n">
+      <c r="F20">
         <v>0.0269</v>
       </c>
     </row>
@@ -1001,10 +939,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E21" t="n">
+      <c r="E21">
         <v>0.0172</v>
       </c>
-      <c r="F21" t="n">
+      <c r="F21">
         <v>0.0256</v>
       </c>
     </row>
@@ -1029,10 +967,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>0.0151</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F22">
         <v>0.0224</v>
       </c>
     </row>
@@ -1057,10 +995,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E23" t="n">
+      <c r="E23">
         <v>0.0167</v>
       </c>
-      <c r="F23" t="n">
+      <c r="F23">
         <v>0.0247</v>
       </c>
     </row>
@@ -1085,10 +1023,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>0.0173</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>0.0259</v>
       </c>
     </row>
@@ -1113,10 +1051,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>0.0192</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>0.0279</v>
       </c>
     </row>
@@ -1141,10 +1079,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>0.0174</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F26">
         <v>0.0262</v>
       </c>
     </row>
@@ -1169,10 +1107,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27">
         <v>0.0175</v>
       </c>
-      <c r="F27" t="n">
+      <c r="F27">
         <v>0.0256</v>
       </c>
     </row>
@@ -1197,10 +1135,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E28" t="n">
+      <c r="E28">
         <v>0.0167</v>
       </c>
-      <c r="F28" t="n">
+      <c r="F28">
         <v>0.0251</v>
       </c>
     </row>
@@ -1225,10 +1163,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E29" t="n">
+      <c r="E29">
         <v>0.0173</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F29">
         <v>0.0259</v>
       </c>
     </row>
@@ -1253,10 +1191,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E30" t="n">
+      <c r="E30">
         <v>0.0166</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F30">
         <v>0.0255</v>
       </c>
     </row>
@@ -1281,10 +1219,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E31" t="n">
+      <c r="E31">
         <v>0.0176</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F31">
         <v>0.0256</v>
       </c>
     </row>
@@ -1309,10 +1247,10 @@
           <t>WITS</t>
         </is>
       </c>
-      <c r="E32" t="n">
+      <c r="E32">
         <v>0.0185</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F32">
         <v>0.0271</v>
       </c>
     </row>
@@ -1337,10 +1275,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E33" t="n">
+      <c r="E33">
         <v>0.0181</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F33">
         <v>0.0269</v>
       </c>
     </row>
@@ -1365,10 +1303,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E34" t="n">
+      <c r="E34">
         <v>0.0165</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F34">
         <v>0.0245</v>
       </c>
     </row>
@@ -1393,10 +1331,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E35" t="n">
+      <c r="E35">
         <v>0.017</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F35">
         <v>0.0248</v>
       </c>
     </row>
@@ -1421,10 +1359,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>0.0176</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F36">
         <v>0.0266</v>
       </c>
     </row>
@@ -1449,10 +1387,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E37" t="n">
+      <c r="E37">
         <v>0.0178</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F37">
         <v>0.0264</v>
       </c>
     </row>
@@ -1477,10 +1415,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E38" t="n">
+      <c r="E38">
         <v>0.0183</v>
       </c>
-      <c r="F38" t="n">
+      <c r="F38">
         <v>0.0272</v>
       </c>
     </row>
@@ -1505,10 +1443,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E39" t="n">
+      <c r="E39">
         <v>0.018</v>
       </c>
-      <c r="F39" t="n">
+      <c r="F39">
         <v>0.0275</v>
       </c>
     </row>
@@ -1533,10 +1471,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E40" t="n">
+      <c r="E40">
         <v>0.0175</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F40">
         <v>0.026</v>
       </c>
     </row>
@@ -1561,10 +1499,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E41" t="n">
+      <c r="E41">
         <v>0.0153</v>
       </c>
-      <c r="F41" t="n">
+      <c r="F41">
         <v>0.0231</v>
       </c>
     </row>
@@ -1589,10 +1527,10 @@
           <t>UV</t>
         </is>
       </c>
-      <c r="E42" t="n">
+      <c r="E42">
         <v>0.017</v>
       </c>
-      <c r="F42" t="n">
+      <c r="F42">
         <v>0.0257</v>
       </c>
     </row>
@@ -1617,10 +1555,10 @@
           <t>UNI-FI</t>
         </is>
       </c>
-      <c r="E43" t="n">
+      <c r="E43">
         <v>0.0162</v>
       </c>
-      <c r="F43" t="n">
+      <c r="F43">
         <v>0.0247</v>
       </c>
     </row>
@@ -1645,10 +1583,10 @@
           <t>UNI-FI</t>
         </is>
       </c>
-      <c r="E44" t="n">
+      <c r="E44">
         <v>0.0158</v>
       </c>
-      <c r="F44" t="n">
+      <c r="F44">
         <v>0.0238</v>
       </c>
     </row>
@@ -1673,10 +1611,10 @@
           <t>UNI-FI</t>
         </is>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>0.0144</v>
       </c>
-      <c r="F45" t="n">
+      <c r="F45">
         <v>0.0219</v>
       </c>
     </row>
@@ -1701,10 +1639,10 @@
           <t>UNI-FI</t>
         </is>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>0.0167</v>
       </c>
-      <c r="F46" t="n">
+      <c r="F46">
         <v>0.0244</v>
       </c>
     </row>
@@ -1729,10 +1667,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>0.0055</v>
       </c>
-      <c r="F47" t="n">
+      <c r="F47">
         <v>0.0092</v>
       </c>
     </row>
@@ -1757,10 +1695,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>0.0052</v>
       </c>
-      <c r="F48" t="n">
+      <c r="F48">
         <v>0.0089</v>
       </c>
     </row>
@@ -1785,10 +1723,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>0.0072</v>
       </c>
-      <c r="F49" t="n">
+      <c r="F49">
         <v>0.0112</v>
       </c>
     </row>
@@ -1813,10 +1751,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E50" t="n">
+      <c r="E50">
         <v>0.0065</v>
       </c>
-      <c r="F50" t="n">
+      <c r="F50">
         <v>0.0105</v>
       </c>
     </row>
@@ -1841,10 +1779,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E51" t="n">
+      <c r="E51">
         <v>0.0065</v>
       </c>
-      <c r="F51" t="n">
+      <c r="F51">
         <v>0.0104</v>
       </c>
     </row>
@@ -1869,10 +1807,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E52" t="n">
+      <c r="E52">
         <v>0.0053</v>
       </c>
-      <c r="F52" t="n">
+      <c r="F52">
         <v>0.008999999999999999</v>
       </c>
     </row>
@@ -1897,10 +1835,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E53" t="n">
+      <c r="E53">
         <v>0.0037</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F53">
         <v>0.0068</v>
       </c>
     </row>
@@ -1925,10 +1863,10 @@
           <t>MRAC</t>
         </is>
       </c>
-      <c r="E54" t="n">
+      <c r="E54">
         <v>0.0078</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F54">
         <v>0.0121</v>
       </c>
     </row>
@@ -1953,10 +1891,10 @@
           <t>MRAC</t>
         </is>
       </c>
-      <c r="E55" t="n">
+      <c r="E55">
         <v>0.0062</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F55">
         <v>0.0103</v>
       </c>
     </row>
@@ -1981,10 +1919,10 @@
           <t>MRAC</t>
         </is>
       </c>
-      <c r="E56" t="n">
+      <c r="E56">
         <v>0.0047</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F56">
         <v>0.0083</v>
       </c>
     </row>
@@ -2009,10 +1947,10 @@
           <t>MRAC</t>
         </is>
       </c>
-      <c r="E57" t="n">
+      <c r="E57">
         <v>0.008800000000000001</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F57">
         <v>0.0135</v>
       </c>
     </row>
@@ -2037,10 +1975,10 @@
           <t>MRAC</t>
         </is>
       </c>
-      <c r="E58" t="n">
+      <c r="E58">
         <v>0.0063</v>
       </c>
-      <c r="F58" t="n">
+      <c r="F58">
         <v>0.0102</v>
       </c>
     </row>
@@ -2065,10 +2003,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E59" t="n">
+      <c r="E59">
         <v>0.008500000000000001</v>
       </c>
-      <c r="F59" t="n">
+      <c r="F59">
         <v>0.0127</v>
       </c>
     </row>
@@ -2093,10 +2031,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E60" t="n">
+      <c r="E60">
         <v>0.007900000000000001</v>
       </c>
-      <c r="F60" t="n">
+      <c r="F60">
         <v>0.0124</v>
       </c>
     </row>
@@ -2121,10 +2059,10 @@
           <t>ZMB</t>
         </is>
       </c>
-      <c r="E61" t="n">
+      <c r="E61">
         <v>0.0092</v>
       </c>
-      <c r="F61" t="n">
+      <c r="F61">
         <v>0.0128</v>
       </c>
     </row>
@@ -2149,10 +2087,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E62" t="n">
+      <c r="E62">
         <v>0.008399999999999999</v>
       </c>
-      <c r="F62" t="n">
+      <c r="F62">
         <v>0.013</v>
       </c>
     </row>
@@ -2177,10 +2115,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E63" t="n">
+      <c r="E63">
         <v>0.0003</v>
       </c>
-      <c r="F63" t="n">
+      <c r="F63">
         <v>0.001</v>
       </c>
     </row>
@@ -2205,10 +2143,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E64" t="n">
+      <c r="E64">
         <v>0.0025</v>
       </c>
-      <c r="F64" t="n">
+      <c r="F64">
         <v>0.0052</v>
       </c>
     </row>
@@ -2233,10 +2171,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E65" t="n">
+      <c r="E65">
         <v>0.0001</v>
       </c>
-      <c r="F65" t="n">
+      <c r="F65">
         <v>0.0004</v>
       </c>
     </row>
@@ -2261,10 +2199,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E66" t="n">
+      <c r="E66">
         <v>0.0012</v>
       </c>
-      <c r="F66" t="n">
+      <c r="F66">
         <v>0.003</v>
       </c>
     </row>
@@ -2289,10 +2227,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E67" t="n">
+      <c r="E67">
         <v>0.0014</v>
       </c>
-      <c r="F67" t="n">
+      <c r="F67">
         <v>0.0036</v>
       </c>
     </row>
@@ -2317,10 +2255,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E68" t="n">
+      <c r="E68">
         <v>0</v>
       </c>
-      <c r="F68" t="n">
+      <c r="F68">
         <v>0.0002</v>
       </c>
     </row>
@@ -2345,10 +2283,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E69" t="n">
+      <c r="E69">
         <v>0.0005999999999999999</v>
       </c>
-      <c r="F69" t="n">
+      <c r="F69">
         <v>0.0019</v>
       </c>
     </row>
@@ -2373,10 +2311,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E70" t="n">
+      <c r="E70">
         <v>0.0014</v>
       </c>
-      <c r="F70" t="n">
+      <c r="F70">
         <v>0.0034</v>
       </c>
     </row>
@@ -2401,10 +2339,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>0.0003</v>
       </c>
-      <c r="F71" t="n">
+      <c r="F71">
         <v>0.001</v>
       </c>
     </row>
@@ -2429,10 +2367,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>0.0017</v>
       </c>
-      <c r="F72" t="n">
+      <c r="F72">
         <v>0.0038</v>
       </c>
     </row>
@@ -2457,10 +2395,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E73" t="n">
+      <c r="E73">
         <v>0.0044</v>
       </c>
-      <c r="F73" t="n">
+      <c r="F73">
         <v>0.0075</v>
       </c>
     </row>
@@ -2485,10 +2423,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E74" t="n">
+      <c r="E74">
         <v>0.0025</v>
       </c>
-      <c r="F74" t="n">
+      <c r="F74">
         <v>0.0048</v>
       </c>
     </row>
@@ -2513,10 +2451,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E75" t="n">
+      <c r="E75">
         <v>0.0035</v>
       </c>
-      <c r="F75" t="n">
+      <c r="F75">
         <v>0.0065</v>
       </c>
     </row>
@@ -2541,10 +2479,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E76" t="n">
+      <c r="E76">
         <v>0.0039</v>
       </c>
-      <c r="F76" t="n">
+      <c r="F76">
         <v>0.007</v>
       </c>
     </row>
@@ -2569,10 +2507,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E77" t="n">
+      <c r="E77">
         <v>0.0043</v>
       </c>
-      <c r="F77" t="n">
+      <c r="F77">
         <v>0.0077</v>
       </c>
     </row>
@@ -2597,10 +2535,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E78" t="n">
+      <c r="E78">
         <v>0.01</v>
       </c>
-      <c r="F78" t="n">
+      <c r="F78">
         <v>0.0155</v>
       </c>
     </row>
@@ -2625,10 +2563,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E79" t="n">
+      <c r="E79">
         <v>0.0076</v>
       </c>
-      <c r="F79" t="n">
+      <c r="F79">
         <v>0.0129</v>
       </c>
     </row>
@@ -2653,10 +2591,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E80" t="n">
+      <c r="E80">
         <v>0.0076</v>
       </c>
-      <c r="F80" t="n">
+      <c r="F80">
         <v>0.0125</v>
       </c>
     </row>
@@ -2681,10 +2619,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E81" t="n">
+      <c r="E81">
         <v>0.0086</v>
       </c>
-      <c r="F81" t="n">
+      <c r="F81">
         <v>0.0134</v>
       </c>
     </row>
@@ -2709,10 +2647,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>0.008399999999999999</v>
       </c>
-      <c r="F82" t="n">
+      <c r="F82">
         <v>0.013</v>
       </c>
     </row>
@@ -2737,10 +2675,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E83" t="n">
+      <c r="E83">
         <v>0.0039</v>
       </c>
-      <c r="F83" t="n">
+      <c r="F83">
         <v>0.0074</v>
       </c>
     </row>
@@ -2765,10 +2703,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E84" t="n">
+      <c r="E84">
         <v>0.008500000000000001</v>
       </c>
-      <c r="F84" t="n">
+      <c r="F84">
         <v>0.0156</v>
       </c>
     </row>
@@ -2793,10 +2731,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E85" t="n">
+      <c r="E85">
         <v>0.0076</v>
       </c>
-      <c r="F85" t="n">
+      <c r="F85">
         <v>0.0115</v>
       </c>
     </row>
@@ -2821,10 +2759,10 @@
           <t>UM-APC</t>
         </is>
       </c>
-      <c r="E86" t="n">
+      <c r="E86">
         <v>0.009599999999999999</v>
       </c>
-      <c r="F86" t="n">
+      <c r="F86">
         <v>0.0148</v>
       </c>
     </row>
@@ -2849,10 +2787,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E87" t="n">
+      <c r="E87">
         <v>0.0081</v>
       </c>
-      <c r="F87" t="n">
+      <c r="F87">
         <v>0.0127</v>
       </c>
     </row>
@@ -2877,10 +2815,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E88" t="n">
+      <c r="E88">
         <v>0.007900000000000001</v>
       </c>
-      <c r="F88" t="n">
+      <c r="F88">
         <v>0.0128</v>
       </c>
     </row>
@@ -2905,10 +2843,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E89" t="n">
+      <c r="E89">
         <v>0.008500000000000001</v>
       </c>
-      <c r="F89" t="n">
+      <c r="F89">
         <v>0.0135</v>
       </c>
     </row>
@@ -2933,10 +2871,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>0.0081</v>
       </c>
-      <c r="F90" t="n">
+      <c r="F90">
         <v>0.013</v>
       </c>
     </row>
@@ -2961,10 +2899,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>0.0077</v>
       </c>
-      <c r="F91" t="n">
+      <c r="F91">
         <v>0.0124</v>
       </c>
     </row>
@@ -2989,10 +2927,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>0.008399999999999999</v>
       </c>
-      <c r="F92" t="n">
+      <c r="F92">
         <v>0.0131</v>
       </c>
     </row>
@@ -3017,10 +2955,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E93" t="n">
+      <c r="E93">
         <v>0.0071</v>
       </c>
-      <c r="F93" t="n">
+      <c r="F93">
         <v>0.0115</v>
       </c>
     </row>
@@ -3045,10 +2983,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E94" t="n">
+      <c r="E94">
         <v>0.008399999999999999</v>
       </c>
-      <c r="F94" t="n">
+      <c r="F94">
         <v>0.013</v>
       </c>
     </row>
@@ -3073,10 +3011,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E95" t="n">
+      <c r="E95">
         <v>0.0073</v>
       </c>
-      <c r="F95" t="n">
+      <c r="F95">
         <v>0.0121</v>
       </c>
     </row>
@@ -3101,10 +3039,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E96" t="n">
+      <c r="E96">
         <v>0.0073</v>
       </c>
-      <c r="F96" t="n">
+      <c r="F96">
         <v>0.0122</v>
       </c>
     </row>
@@ -3129,10 +3067,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E97" t="n">
+      <c r="E97">
         <v>0.0062</v>
       </c>
-      <c r="F97" t="n">
+      <c r="F97">
         <v>0.0111</v>
       </c>
     </row>
@@ -3157,10 +3095,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E98" t="n">
+      <c r="E98">
         <v>0.0058</v>
       </c>
-      <c r="F98" t="n">
+      <c r="F98">
         <v>0.0104</v>
       </c>
     </row>
@@ -3185,10 +3123,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E99" t="n">
+      <c r="E99">
         <v>0.0072</v>
       </c>
-      <c r="F99" t="n">
+      <c r="F99">
         <v>0.0123</v>
       </c>
     </row>
@@ -3213,10 +3151,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E100" t="n">
+      <c r="E100">
         <v>0.007900000000000001</v>
       </c>
-      <c r="F100" t="n">
+      <c r="F100">
         <v>0.0131</v>
       </c>
     </row>
@@ -3241,10 +3179,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E101" t="n">
+      <c r="E101">
         <v>0.0081</v>
       </c>
-      <c r="F101" t="n">
+      <c r="F101">
         <v>0.013</v>
       </c>
     </row>
@@ -3269,10 +3207,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E102" t="n">
+      <c r="E102">
         <v>0.0134</v>
       </c>
-      <c r="F102" t="n">
+      <c r="F102">
         <v>0.0188</v>
       </c>
     </row>
@@ -3297,10 +3235,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E103" t="n">
+      <c r="E103">
         <v>0.0118</v>
       </c>
-      <c r="F103" t="n">
+      <c r="F103">
         <v>0.0165</v>
       </c>
     </row>
@@ -3325,10 +3263,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E104" t="n">
+      <c r="E104">
         <v>0.0133</v>
       </c>
-      <c r="F104" t="n">
+      <c r="F104">
         <v>0.0194</v>
       </c>
     </row>
@@ -3353,10 +3291,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E105" t="n">
+      <c r="E105">
         <v>0.0117</v>
       </c>
-      <c r="F105" t="n">
+      <c r="F105">
         <v>0.0173</v>
       </c>
     </row>
@@ -3381,10 +3319,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E106" t="n">
+      <c r="E106">
         <v>0.0135</v>
       </c>
-      <c r="F106" t="n">
+      <c r="F106">
         <v>0.0188</v>
       </c>
     </row>
@@ -3409,10 +3347,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E107" t="n">
+      <c r="E107">
         <v>0.0123</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F107">
         <v>0.0173</v>
       </c>
     </row>
@@ -3437,10 +3375,10 @@
           <t>NMW</t>
         </is>
       </c>
-      <c r="E108" t="n">
+      <c r="E108">
         <v>0.012</v>
       </c>
-      <c r="F108" t="n">
+      <c r="F108">
         <v>0.0174</v>
       </c>
     </row>
@@ -3465,10 +3403,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E109" t="n">
+      <c r="E109">
         <v>0.0035</v>
       </c>
-      <c r="F109" t="n">
+      <c r="F109">
         <v>0.0065</v>
       </c>
     </row>
@@ -3493,10 +3431,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E110" t="n">
+      <c r="E110">
         <v>0.003</v>
       </c>
-      <c r="F110" t="n">
+      <c r="F110">
         <v>0.0059</v>
       </c>
     </row>
@@ -3521,10 +3459,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E111" t="n">
+      <c r="E111">
         <v>0.0026</v>
       </c>
-      <c r="F111" t="n">
+      <c r="F111">
         <v>0.0053</v>
       </c>
     </row>
@@ -3549,10 +3487,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E112" t="n">
+      <c r="E112">
         <v>0.0022</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F112">
         <v>0.0046</v>
       </c>
     </row>
@@ -3577,10 +3515,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E113" t="n">
+      <c r="E113">
         <v>0.0022</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F113">
         <v>0.0045</v>
       </c>
     </row>
@@ -3605,10 +3543,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E114" t="n">
+      <c r="E114">
         <v>0.0017</v>
       </c>
-      <c r="F114" t="n">
+      <c r="F114">
         <v>0.0037</v>
       </c>
     </row>
@@ -3633,10 +3571,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E115" t="n">
+      <c r="E115">
         <v>0.0015</v>
       </c>
-      <c r="F115" t="n">
+      <c r="F115">
         <v>0.0033</v>
       </c>
     </row>
@@ -3661,10 +3599,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E116" t="n">
+      <c r="E116">
         <v>0.0038</v>
       </c>
-      <c r="F116" t="n">
+      <c r="F116">
         <v>0.0069</v>
       </c>
     </row>
@@ -3689,10 +3627,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E117" t="n">
+      <c r="E117">
         <v>0.0012</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F117">
         <v>0.0029</v>
       </c>
     </row>
@@ -3717,10 +3655,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E118" t="n">
+      <c r="E118">
         <v>0.013</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F118">
         <v>0.0216</v>
       </c>
     </row>
@@ -3745,10 +3683,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E119" t="n">
+      <c r="E119">
         <v>0.0108</v>
       </c>
-      <c r="F119" t="n">
+      <c r="F119">
         <v>0.0183</v>
       </c>
     </row>
@@ -3773,10 +3711,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E120" t="n">
+      <c r="E120">
         <v>0.0109</v>
       </c>
-      <c r="F120" t="n">
+      <c r="F120">
         <v>0.0183</v>
       </c>
     </row>
@@ -3801,10 +3739,10 @@
           <t>HMNH</t>
         </is>
       </c>
-      <c r="E121" t="n">
+      <c r="E121">
         <v>0.0073</v>
       </c>
-      <c r="F121" t="n">
+      <c r="F121">
         <v>0.0122</v>
       </c>
     </row>
@@ -3829,10 +3767,10 @@
           <t>YPM</t>
         </is>
       </c>
-      <c r="E122" t="n">
+      <c r="E122">
         <v>0.0073</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F122">
         <v>0.0125</v>
       </c>
     </row>
@@ -3857,10 +3795,10 @@
           <t>YPM</t>
         </is>
       </c>
-      <c r="E123" t="n">
+      <c r="E123">
         <v>0.0134</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F123">
         <v>0.0224</v>
       </c>
     </row>
@@ -3885,10 +3823,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E124" t="n">
+      <c r="E124">
         <v>0.0144</v>
       </c>
-      <c r="F124" t="n">
+      <c r="F124">
         <v>0.0221</v>
       </c>
     </row>
@@ -3913,10 +3851,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E125" t="n">
+      <c r="E125">
         <v>0.0129</v>
       </c>
-      <c r="F125" t="n">
+      <c r="F125">
         <v>0.0204</v>
       </c>
     </row>
@@ -3941,10 +3879,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E126" t="n">
+      <c r="E126">
         <v>0.0128</v>
       </c>
-      <c r="F126" t="n">
+      <c r="F126">
         <v>0.0216</v>
       </c>
     </row>
@@ -3969,10 +3907,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E127" t="n">
+      <c r="E127">
         <v>0.0118</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F127">
         <v>0.0202</v>
       </c>
     </row>
@@ -3997,10 +3935,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E128" t="n">
+      <c r="E128">
         <v>0.0122</v>
       </c>
-      <c r="F128" t="n">
+      <c r="F128">
         <v>0.0189</v>
       </c>
     </row>
@@ -4025,10 +3963,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E129" t="n">
+      <c r="E129">
         <v>0.0118</v>
       </c>
-      <c r="F129" t="n">
+      <c r="F129">
         <v>0.019</v>
       </c>
     </row>
@@ -4053,10 +3991,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E130" t="n">
+      <c r="E130">
         <v>0.0118</v>
       </c>
-      <c r="F130" t="n">
+      <c r="F130">
         <v>0.0202</v>
       </c>
     </row>
@@ -4081,10 +4019,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E131" t="n">
+      <c r="E131">
         <v>0.0105</v>
       </c>
-      <c r="F131" t="n">
+      <c r="F131">
         <v>0.018</v>
       </c>
     </row>
@@ -4109,10 +4047,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E132" t="n">
+      <c r="E132">
         <v>0.013</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F132">
         <v>0.0213</v>
       </c>
     </row>
@@ -4137,10 +4075,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E133" t="n">
+      <c r="E133">
         <v>0.008200000000000001</v>
       </c>
-      <c r="F133" t="n">
+      <c r="F133">
         <v>0.0162</v>
       </c>
     </row>
@@ -4165,10 +4103,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E134" t="n">
+      <c r="E134">
         <v>0.0086</v>
       </c>
-      <c r="F134" t="n">
+      <c r="F134">
         <v>0.0162</v>
       </c>
     </row>
@@ -4193,10 +4131,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E135" t="n">
+      <c r="E135">
         <v>0.008699999999999999</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F135">
         <v>0.0169</v>
       </c>
     </row>
@@ -4221,10 +4159,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E136" t="n">
+      <c r="E136">
         <v>0.0097</v>
       </c>
-      <c r="F136" t="n">
+      <c r="F136">
         <v>0.0181</v>
       </c>
     </row>
@@ -4249,10 +4187,10 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E137" t="n">
+      <c r="E137">
         <v>0.0089</v>
       </c>
-      <c r="F137" t="n">
+      <c r="F137">
         <v>0.0169</v>
       </c>
     </row>
@@ -4277,15 +4215,15 @@
           <t>AMNH</t>
         </is>
       </c>
-      <c r="E138" t="n">
+      <c r="E138">
         <v>0.0091</v>
       </c>
-      <c r="F138" t="n">
+      <c r="F138">
         <v>0.0172</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -4565,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{53E847A7-E41A-40FE-A6C8-3A31F8569A42}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3D234ED-0AB9-497C-A765-B874F0AD26FA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6CD27C9B-3C50-48E1-883F-FBD466CD3328}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818EE5A2-35E2-43CD-8760-64214B4A54BB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{564F5D96-EC9D-4760-ADA9-6922E09E2A9C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CEAC807-79F9-4A5B-A9D7-4E9FF4AAE4BB}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3D234ED-0AB9-497C-A765-B874F0AD26FA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95CE3D07-0F1F-4E59-A6E5-9F03FCAA1720}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{818EE5A2-35E2-43CD-8760-64214B4A54BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30718EB4-BDC4-4B73-A0C1-01A43B4B8A0C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7CEAC807-79F9-4A5B-A9D7-4E9FF4AAE4BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6572C9F8-0925-4830-9DA5-040F603587C1}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95CE3D07-0F1F-4E59-A6E5-9F03FCAA1720}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DB542B9-94D8-4989-8E07-56A83D1E5005}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{30718EB4-BDC4-4B73-A0C1-01A43B4B8A0C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03614CEA-A99A-4FC1-AD4E-0E5C6D3F27C8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6572C9F8-0925-4830-9DA5-040F603587C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{917E90E7-8651-4C75-9A2B-BE4DAE16EB08}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DB542B9-94D8-4989-8E07-56A83D1E5005}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00262DAA-1DF0-4F49-A321-796E4959CC35}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03614CEA-A99A-4FC1-AD4E-0E5C6D3F27C8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BC2CB3A-774C-4DC3-B0F6-45713B3A7295}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{917E90E7-8651-4C75-9A2B-BE4DAE16EB08}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12510E49-463D-4F07-A546-821D739453BB}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{00262DAA-1DF0-4F49-A321-796E4959CC35}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C11B9F9E-B15E-4F53-921F-18E581AE52C2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7BC2CB3A-774C-4DC3-B0F6-45713B3A7295}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02C988E6-EC67-4B6C-9530-BDF3B05A5E77}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12510E49-463D-4F07-A546-821D739453BB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38FC6ACF-A685-4F78-AFCD-315DE50C4A2E}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C11B9F9E-B15E-4F53-921F-18E581AE52C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B7D7567-0A3A-4FF8-9790-3F7D672206D7}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02C988E6-EC67-4B6C-9530-BDF3B05A5E77}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB74C8E-FC59-4EA5-B874-B2A086D59D68}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38FC6ACF-A685-4F78-AFCD-315DE50C4A2E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A8B8AD-8774-41A7-B60C-5C15C0CAB7D5}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B7D7567-0A3A-4FF8-9790-3F7D672206D7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEF97665-0202-4C26-B56E-7945D0F2D452}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB74C8E-FC59-4EA5-B874-B2A086D59D68}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5EB9F4F-AA78-4C5D-8D2C-41244E5E7F63}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{37A8B8AD-8774-41A7-B60C-5C15C0CAB7D5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F4E1F73-BC82-456F-9BC6-81DEC83FF311}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEF97665-0202-4C26-B56E-7945D0F2D452}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03FC7F65-23F1-4E4F-AB6A-B4C0B4C60D7B}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5EB9F4F-AA78-4C5D-8D2C-41244E5E7F63}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C227C4-427E-4AD2-A083-EF78F833C281}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F4E1F73-BC82-456F-9BC6-81DEC83FF311}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35EBB788-3EFF-47CB-9D14-E4C6A0914DB2}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03FC7F65-23F1-4E4F-AB6A-B4C0B4C60D7B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64AED997-2709-453E-BE14-529F1529C956}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25C227C4-427E-4AD2-A083-EF78F833C281}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D44EB586-CF8D-4D18-9DE1-546F7A30E8B3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35EBB788-3EFF-47CB-9D14-E4C6A0914DB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC4A27A3-2F08-4B90-BA7C-51F80D99F8E6}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{64AED997-2709-453E-BE14-529F1529C956}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5791361-242A-4119-9993-75EBD645CF8C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D44EB586-CF8D-4D18-9DE1-546F7A30E8B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8D467E-A079-4295-AE08-516EC9059B39}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC4A27A3-2F08-4B90-BA7C-51F80D99F8E6}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1795504E-1848-4516-83BA-93C5BF8D1C0E}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B5791361-242A-4119-9993-75EBD645CF8C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{881FAF54-1208-4C82-9528-4FE24B3BAA48}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B8D467E-A079-4295-AE08-516EC9059B39}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E10BCC-519C-4B9F-8086-2EBA233FF167}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1795504E-1848-4516-83BA-93C5BF8D1C0E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDAD5F1B-D34A-408E-BB2B-DF3DF93D1CEB}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{881FAF54-1208-4C82-9528-4FE24B3BAA48}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD43206-4EA9-4675-BAE2-12A8D93AB085}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82E10BCC-519C-4B9F-8086-2EBA233FF167}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB9E0A9-60F4-4259-827D-159B085003F0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDAD5F1B-D34A-408E-BB2B-DF3DF93D1CEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160E7158-E0CF-4AF1-AF5A-E4A92CFBF6D0}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2FD43206-4EA9-4675-BAE2-12A8D93AB085}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA6E281-BD52-4A1C-AF2C-6F2F9F3FB1B3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAB9E0A9-60F4-4259-827D-159B085003F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEDB9880-4FB8-456B-B103-52C97E2AA06D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{160E7158-E0CF-4AF1-AF5A-E4A92CFBF6D0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE2E41D4-298E-4EC0-A069-E86036CF98C9}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DA6E281-BD52-4A1C-AF2C-6F2F9F3FB1B3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF073689-E991-40B8-BC0D-6E26B013E080}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BEDB9880-4FB8-456B-B103-52C97E2AA06D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6147666-AF4A-4BE5-B396-A192A0EFCA47}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE2E41D4-298E-4EC0-A069-E86036CF98C9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8C1115D-AFAD-496B-9C48-504C9101CE69}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF073689-E991-40B8-BC0D-6E26B013E080}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE964D2D-2603-4B52-9ADA-029AE54A1063}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6147666-AF4A-4BE5-B396-A192A0EFCA47}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15DDF7C4-B5FC-4E75-A4F5-7A7A44E8E741}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A8C1115D-AFAD-496B-9C48-504C9101CE69}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68FF737-C85B-4579-8607-E928A98C641D}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE964D2D-2603-4B52-9ADA-029AE54A1063}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F509DB9-4FAA-4B8A-BA1A-B14F1B6A8EE8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{15DDF7C4-B5FC-4E75-A4F5-7A7A44E8E741}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB4E89A-0787-45D0-AD37-34D1CAE31E11}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B68FF737-C85B-4579-8607-E928A98C641D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB45273-F244-4470-8C02-DEA83C08FB3A}"/>
 </file>
--- a/____EvoM1_TraitTable/hand_liu.xlsx
+++ b/____EvoM1_TraitTable/hand_liu.xlsx
@@ -4503,13 +4503,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F509DB9-4FAA-4B8A-BA1A-B14F1B6A8EE8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8A3A20B-4A59-4074-8EAF-EC13010843BA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCB4E89A-0787-45D0-AD37-34D1CAE31E11}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2B9A8553-7980-4A05-9669-5EFD877E85BE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CB45273-F244-4470-8C02-DEA83C08FB3A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E162B22A-52C5-4D7B-9D3A-32FBBF22A064}"/>
 </file>